--- a/docs/qa/P4-화면테스트_v1.1.xlsx
+++ b/docs/qa/P4-화면테스트_v1.1.xlsx
@@ -2827,7 +2827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2842,6 +2842,9 @@
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2905,6 +2908,21 @@
           <t xml:space="preserve">담당</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재확인 판정(10/11 main b95a424)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재확인 결과</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재확인 증거</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2967,6 +2985,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3029,6 +3050,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3091,6 +3115,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3149,6 +3176,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3211,6 +3241,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3273,6 +3306,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3323,7 +3359,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미확인. 구독이 있는 기기(WY-qa2 웹 푸시 구독 뒤 로그아웃)에서 확인 필요</t>
+          <t xml:space="preserve">미확인. 구독이 있는 기기(WY-qa2 웹 푸시 구독 뒤 로그아웃)에서 확인 필요 / REL 때 실기기(사용자 카드 1500: 앱 테스트는 나중에)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3331,6 +3367,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3393,6 +3432,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3455,6 +3497,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3517,6 +3562,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3575,6 +3623,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3633,6 +3684,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3683,7 +3737,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미확인(운영 점검 모드는 켜지 않음). 로컬 dev:mock 확인은 P4-premerge 증거</t>
+          <t xml:space="preserve">미확인(운영 점검 모드는 켜지 않음). 로컬 dev:mock 확인은 P4-premerge 증거 / REL 때 실기기(사용자 카드 1500: 앱 테스트는 나중에)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3691,6 +3745,9 @@
           <t xml:space="preserve">WY-qa</t>
         </is>
       </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3753,6 +3810,9 @@
           <t xml:space="preserve">WY-qa2</t>
         </is>
       </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3807,7 +3867,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미확인. 데이터 많은 계정으로 확인 필요</t>
+          <t xml:space="preserve">미확인. 데이터 많은 계정으로 확인 필요 / REL 때 실기기(사용자 카드 1500: 앱 테스트는 나중에)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -3815,6 +3875,9 @@
           <t xml:space="preserve">WY-qa2</t>
         </is>
       </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3877,6 +3940,9 @@
           <t xml:space="preserve">WY-qa2</t>
         </is>
       </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3939,6 +4005,21 @@
           <t xml:space="preserve">WY-qa2</t>
         </is>
       </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">390·1280 복원 토스트 [되돌리기] 80×44, [보기] 44×44(::after·::before 없음, 보이는 크기 기준). 빠른 기록 토스트 [되돌리기] 80×44</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evidence/P4-prod-recheck/toast-restore-390.png, evidence/P4-prod-recheck/toast-restore-1280.png, evidence/P4-prod-recheck/toast-quick-390.png</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3997,6 +4078,9 @@
           <t xml:space="preserve">WY-qa2</t>
         </is>
       </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4047,7 +4131,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미확인(알림이 쌓인 계정 필요)</t>
+          <t xml:space="preserve">미확인(알림이 쌓인 계정 필요) / REL 때 실기기(사용자 카드 1500: 앱 테스트는 나중에)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4055,6 +4139,9 @@
           <t xml:space="preserve">WY-qa2</t>
         </is>
       </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4113,6 +4200,9 @@
           <t xml:space="preserve">WY-qa2</t>
         </is>
       </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4167,7 +4257,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미확인. 실제 Chrome 데스크톱·설치 기기 확인 필요(로그아웃 시 구독 해제 포함)</t>
+          <t xml:space="preserve">미확인. 실제 Chrome 데스크톱·설치 기기 확인 필요(로그아웃 시 구독 해제 포함) / REL 때 실기기(사용자 카드 1500: 앱 테스트는 나중에)</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4175,6 +4265,9 @@
           <t xml:space="preserve">WY-qa2</t>
         </is>
       </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4233,6 +4326,9 @@
           <t xml:space="preserve">WY-qa2</t>
         </is>
       </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4295,6 +4391,21 @@
           <t xml:space="preserve">WY-qa2</t>
         </is>
       </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수정 a5b52d8 배포 확인. 1280·390: #FFFFFF/쿨 그레이, #FFF3A0/쿨 그레이·화이트 → 직접 고르기 아래 "이 색은 배경과 너무 비슷해서…더 진한 색을 골라 주세요."(aria-invalid), [저장] aria-disabled, 눌러도 PATCH 없음. [기본값으로]로 안내 사라지고 저장 가능. #3366CC(4.88/5.37) 저장 → "저장했어요. 앱 전체에 적용됐어요". 경계: #949494(2.76/3.03)·#8F8F8F(2.94/3.23) 막힘, #858585 통과 — 배경·흰 표면 중 낮은 쪽 3:1 기준과 일치. 원복(#4B3FD6) 완료</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evidence/P4-prod-recheck/theme-ffffff-쿨 그레이-1280.png, evidence/P4-prod-recheck/theme-fff3a0-화이트-390.png, evidence/P4-prod-recheck/theme-reset-390.png, evidence/P4-prod-recheck/theme-3366cc-saved-1280.png, evidence/P4-prod-recheck/theme-3366cc-saved-390.png</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4353,6 +4464,9 @@
           <t xml:space="preserve">WY-qa2</t>
         </is>
       </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4407,7 +4521,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미확인: 실제 설치 창은 실제 Chrome에서 사용자 확인 필요</t>
+          <t xml:space="preserve">미확인: 실제 설치 창은 실제 Chrome에서 사용자 확인 필요 / REL 때 실기기(사용자 카드 1500: 앱 테스트는 나중에)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4415,9 +4529,77 @@
           <t xml:space="preserve">WY-qa2</t>
         </is>
       </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P4-PROD-R01</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCR-CAL-01</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D-76, D-77</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용성</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">운영 wy-worklog.com 390 (Chromium 터치 에뮬레이션)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1) /calendar/day·week 시간 격자에서 손가락으로 바로 위·아래로 밀기(CDP touch 이벤트)</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세로 스크롤되고 새 일정 범위·창이 생기지 않음(길게 누른 뒤에만 범위 만들기)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일 보기(touch-action pan-y) scrollTop 384→598→104, 주 보기(읽기 전용, auto) 384→598→91. 창·범위 표시 없음</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evidence/P4-prod-recheck/calendar-day-swipe-390.png, evidence/P4-prod-recheck/calendar-week-swipe-390.png</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추가 관찰(febc4bc). iPhone Safari는 범위 밖. 길게 누르기(450ms) 범위 만들기는 시험 안 함</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WY-qa</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L26"/>
+  <autoFilter ref="A1:O27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>